--- a/templates/str_template.xlsx
+++ b/templates/str_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseph.adogeri\Desktop\source\supplemental_tax_rolls_generator\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD44DA4-27CD-451A-8254-1113F0CE2827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD9212A-A41E-4AE9-8DF8-C0F0C9D1466A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1245" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,6 +29,7 @@
     <definedName name="REAL_ESTATE_2" localSheetId="0">20000</definedName>
     <definedName name="REAL_ESTATE_3" localSheetId="0">30000</definedName>
     <definedName name="REAL_ESTATE_4" localSheetId="0">40000</definedName>
+    <definedName name="STR_DATE" localSheetId="0">"AUGUST 21, 2026"</definedName>
     <definedName name="TAX_YEAR" localSheetId="0">2025</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -794,8 +795,8 @@
     </row>
     <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="str">
-        <f ca="1">"AS OF " &amp; UPPER(TEXT(TODAY(), "mmmm d, yyyy"))</f>
-        <v>AS OF AUGUST 20, 2026</v>
+        <f>"AS OF "  &amp; STR_DATE</f>
+        <v>AS OF AUGUST 21, 2026</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/templates/str_template.xlsx
+++ b/templates/str_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseph.adogeri\Desktop\source\supplemental_tax_rolls_generator\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD9212A-A41E-4AE9-8DF8-C0F0C9D1466A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D986258-2B08-44AA-A7EA-D986BCBAF0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1245" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20820" yWindow="5265" windowWidth="16875" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CONSOLIDATED SUMMARY" sheetId="3" r:id="rId1"/>
@@ -972,24 +972,24 @@
         <v>7</v>
       </c>
       <c r="B14" s="24">
-        <f>SUM(B12,ABS(B13))</f>
+        <f>SUM(B12 - ABS(B13))</f>
+        <v>10000</v>
+      </c>
+      <c r="C14" s="24">
+        <f>SUM(C12 - ABS(C13))</f>
+        <v>20000</v>
+      </c>
+      <c r="D14" s="24">
+        <f>SUM(D12 - ABS(D13))</f>
         <v>30000</v>
       </c>
-      <c r="C14" s="24">
-        <f>SUM(C12,ABS(C13))</f>
-        <v>60000</v>
-      </c>
-      <c r="D14" s="24">
-        <f>SUM(D12,ABS(D13))</f>
-        <v>90000</v>
-      </c>
       <c r="E14" s="24">
-        <f>SUM(E12,ABS(E13))</f>
-        <v>120000</v>
+        <f>SUM(E12 - ABS(E13))</f>
+        <v>40000</v>
       </c>
       <c r="F14" s="25">
         <f>SUM(B14:E14)</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="G14" s="14"/>
     </row>
